--- a/expert-system/output/admin/admin.xlsx
+++ b/expert-system/output/admin/admin.xlsx
@@ -16,6 +16,9 @@
     <sheet name="TS-ADM-Settings" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="TS-ADM-Trackers" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="TS-ADM-APIErrors" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TS-ADM-PMTool-Edge" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Test Data" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TS-ADM-PMTool-S15" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Feature Matrix'!$A$3:$I$10</definedName>
@@ -26,6 +29,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'TS-ADM-Settings'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'TS-ADM-Trackers'!$A$3:$J$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'TS-ADM-APIErrors'!$A$3:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'TS-ADM-PMTool-Edge'!$A$3:$J$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'TS-ADM-PMTool-S15'!$A$3:$J$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,8 +96,16 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -147,8 +160,20 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -170,11 +195,61 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -231,6 +306,30 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -597,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -848,82 +947,108 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>TS-ADM-PMTool-Edge</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>PM Tool Integration Edge Cases</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Knowledge Sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1.</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>modules/admin-panel-deep-dive.md — Full code analysis: ProjectController, EmployeeController, CalendarControllerV2, PM Tool sync, 10 design issues</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.</t>
+          <t xml:space="preserve">  1.</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>analysis/admin-calendar-form-validation-rules.md — Field-level DTO validation for calendars, events, salary offices, tracker configuration</t>
+          <t>modules/admin-panel-deep-dive.md — Full code analysis: ProjectController, EmployeeController, CalendarControllerV2, PM Tool sync, 10 design issues</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.</t>
+          <t xml:space="preserve">  2.</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>exploration/ui-flows/admin-panel-pages.md — 7 admin pages: Projects, Employees, TTT Parameters, Calendars, API, Export, Account</t>
+          <t>analysis/admin-calendar-form-validation-rules.md — Field-level DTO validation for calendars, events, salary offices, tracker configuration</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.</t>
+          <t xml:space="preserve">  3.</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>exploration/ui-flows/admin-projects-deep-exploration.md — Project page deep testing: search, filters, detail dialog, tracker data, task templates</t>
+          <t>exploration/ui-flows/admin-panel-pages.md — 7 admin pages: Projects, Employees, TTT Parameters, Calendars, API, Export, Account</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.</t>
+          <t xml:space="preserve">  4.</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>investigations/tracker-integration-deep-dive.md — 8 tracker types, GraalVM sandbox, work log sync, 222K DB rows, 19 credentials</t>
+          <t>exploration/ui-flows/admin-projects-deep-exploration.md — Project page deep testing: search, filters, detail dialog, tracker data, task templates</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">  5.</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>investigations/tracker-integration-deep-dive.md — 8 tracker types, GraalVM sandbox, work log sync, 222K DB rows, 19 credentials</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">  6.</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Qase TIMEREPORT: 0 existing admin panel test cases (no overlap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>Test Data Reference</t>
         </is>
       </c>
     </row>
@@ -931,8 +1056,8 @@
   <mergeCells count="16">
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B25:J25"/>
     <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B25:J25"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="B22:J22"/>
     <mergeCell ref="B23:J23"/>
@@ -953,6 +1078,2212 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId8"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>Suite: PM Tool Edge Cases — Rate Limiting, Failures, Concurrency</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J3" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>TC-ADM-071</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>PM Tool sync — rate limiter boundary (50 req/min)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>PM Tool sync enabled (feature toggle PM_TOOL_SYNC-{env} = ON).
+PM Tool has 60+ projects (more than rate limit allows per minute).</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>1. Trigger manual sync: POST /v1/test/project/sync.
+2. Monitor sync duration.
+3. Verify all projects synced (not just first 50).
+4. DB: SELECT COUNT(*) FROM project WHERE pm_tool_id IS NOT NULL.
+5. Check pm_sync_status for completion record.
+6. Verify no projects dropped due to rate limiting.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>All projects synced despite rate limit — sync takes longer but completes.
+RateLimiter.acquire() blocks thread until permit available (no timeout).
+pm_sync_status shows successful completion.
+No projects missing from sync.</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>#3399</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Admin / PM Tool Sync</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Guava RateLimiter at 50 req/min. acquire() blocks — verify no OOM or timeout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>TC-ADM-072</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool sync — API unavailable (connection timeout)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool sync enabled.
+PM Tool API is unreachable (simulate by changing pmTool.url to invalid host).</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>1. Update PM Tool URL config to unreachable host.
+2. Trigger manual sync: POST /v1/test/project/sync.
+3. Check application logs for error handling.
+4. DB: Verify pm_tool_sync_failed_entity table has entries.
+5. Verify existing project data unchanged.
+6. Check retry batch mechanism activates.</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Sync fails gracefully — no crash or data corruption.
+Failed entities recorded in pm_tool_sync_failed_entity.
+Retry mechanism attempts to re-sync failed entities.
+Existing project data preserved (no deletions on sync failure).</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Admin / PM Tool Sync</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Feign client timeout behavior. Check for proper error logging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>TC-ADM-073</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>PM Tool sync — partial failure (some projects fail, others succeed)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>PM Tool has 10 projects.
+1 project references an employee not in TTT DB.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>1. Trigger sync: POST /v1/test/project/sync.
+2. Check application logs for IllegalStateException.
+3. DB: Verify successfully synced projects are updated.
+4. DB: Check pm_tool_sync_failed_entity for the failing project.
+5. Verify failure is isolated — doesn't abort entire sync.
+6. Check retry: failed project retried in next batch.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>9 of 10 projects sync successfully.
+1 project fails with 500 (missing employee → IllegalStateException).
+Failed project recorded for retry.
+Other projects not affected by the single failure.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>#3384</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Admin / PM Tool Sync</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>PmToolProjectSynchronizer validates employee existence — throws IllegalStateException if missing. Should be business error, not 500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>TC-ADM-074</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool sync — concurrent sync attempts (ShedLock contention)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool sync enabled.
+Cron schedule: every 15 minutes.
+ShedLock configured for sync job.</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>1. Trigger manual sync: POST /v1/test/project/sync.
+2. Immediately trigger second manual sync.
+3. Check application logs for both sync attempts.
+4. Verify ShedLock prevents concurrent execution.
+5. DB: Check shedlock table for lock status.
+6. Verify data consistency — no duplicate projects.</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>First sync acquires ShedLock and runs.
+Second sync either waits or skips (ShedLock behavior).
+No concurrent execution — data integrity maintained.
+No duplicate project entries created.</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Concurrency</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Admin / PM Tool Sync</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>ShedLock prevents concurrent cron execution. Manual trigger may bypass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>TC-ADM-075</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>PM Tool sync — draft project silent ACTIVE conversion</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>PM Tool has a project in 'draft' status.
+Project does not exist in TTT yet.</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>1. Verify project not in TTT: GET /api/ttt/v1/project?name=DraftProject.
+2. Trigger sync: POST /v1/test/project/sync.
+3. GET /api/ttt/v1/project?name=DraftProject.
+4. Check project status in TTT.
+5. Verify no notification sent about status conversion.</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Draft project synced as ACTIVE in TTT.
+No notification to PM/owner about draft→ACTIVE conversion.
+Project appears in employee project lists immediately.
+Design issue: draft projects should not be visible to employees.</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Admin / PM Tool Sync</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Design issue: PmToolProjectSynchronizer silently converts draft→ACTIVE. No feature flag to exclude drafts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>TC-ADM-076</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool sync — pmtId null edge case in UI</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Project synced from PM Tool but pmtId field is null.
+(Legacy project created before pmtId was added)</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>1. DB: Find project with pm_tool_id IS NOT NULL AND pmt_id IS NULL.
+2. Navigate to Admin → Projects page.
+3. Find the project in the table.
+4. Check project name link behavior.
+5. Verify Info modal shows correct data.</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Project name shows as plain text (no link) when pmtId is null.
+No broken link or JavaScript error.
+Info modal displays all available fields correctly.
+href='#' fallback should not trigger page navigation.</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Admin / PM Tool UI</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>tableHelpers.js: pmtId null → falls back to plain text or href='#'. Verify no broken behavior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>TC-ADM-077</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>PM Tool sync — observer batch sync post-processing</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Project has 5 observers (watchers) in PM Tool.
+TTT project has 2 observers.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>1. Record current observers: GET /api/ttt/v1/project/{id}.
+2. Trigger sync: POST /v1/test/project/sync.
+3. GET /api/ttt/v1/project/{id} — check observers.
+4. Verify observers match PM Tool watchers.
+5. DB: Verify project_observer table entries.</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Observers updated to match PM Tool watchers (5 total).
+Old observers not in PM Tool are removed.
+New observers added with correct roles.
+Cache evicted after observer update.</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Admin / PM Tool Sync</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>InternalProjectObserverService handles watcher sync in postProcess().</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>TC-ADM-078</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool sync — sales employee filtering</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool project has:
+- PM: employee type
+- Owner: sales type
+- Supervisor: employee type</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>1. Trigger sync: POST /v1/test/project/sync.
+2. GET /api/ttt/v1/project/{id}.
+3. Check managerId, ownerId, seniorManagerId.
+4. Verify sales person not set as owner in TTT.
+5. Check log for 'removeSalesFromProject' action.</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Sales-type CSToolEntityReference filtered out.
+ownerId = null or previous value (sales person excluded).
+managerId and seniorManagerId set correctly (employee type).
+No error for sales filtering — silent exclusion.</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr"/>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Admin / PM Tool Sync</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>PmToolProjectSynchronizer.removeSalesFromProject() filters by isSales().</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>TC-ADM-079</t>
+        </is>
+      </c>
+      <c r="B12" s="38" t="inlineStr">
+        <is>
+          <t>PM Tool sync — rate limiter custom configuration</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>Spring property pmTool.sync.fetch-rate-per-minute set to 30 (custom value, below default 50).</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="inlineStr">
+        <is>
+          <t>1. Set pmTool.sync.fetch-rate-per-minute=30 in application config
+2. Restart application
+3. Trigger PM Tool sync
+4. Monitor timing between consecutive API calls to PM Tool</t>
+        </is>
+      </c>
+      <c r="E12" s="38" t="inlineStr">
+        <is>
+          <t>Rate limiter enforces ~2 seconds between requests (30 RPM = 0.5 permits/sec). Each fetchRateLimiter.acquire() blocks until permit available. Sync completes slower but without 429 errors.</t>
+        </is>
+      </c>
+      <c r="F12" s="38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G12" s="38" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="H12" s="38" t="inlineStr">
+        <is>
+          <t>#3401</t>
+        </is>
+      </c>
+      <c r="I12" s="38" t="inlineStr">
+        <is>
+          <t>PMTool/Sync</t>
+        </is>
+      </c>
+      <c r="J12" s="38" t="inlineStr">
+        <is>
+          <t>Default: 50 RPM (0.833/sec). Config: @Value("${pmTool.sync.fetch-rate-per-minute:50}"). Not overridden in any config file currently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="39" t="inlineStr">
+        <is>
+          <t>TC-ADM-080</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>PM Tool sync — shared rate limiter across concurrent entity syncs</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="inlineStr">
+        <is>
+          <t>Multiple entity types (projects, employees) sync concurrently through the same PmToolEntitySyncLauncher instance.</t>
+        </is>
+      </c>
+      <c r="D13" s="39" t="inlineStr">
+        <is>
+          <t>1. Trigger full PM Tool sync (projects + related entities)
+2. Monitor total API calls per minute to PM Tool
+3. Verify calls don't exceed configured limit</t>
+        </is>
+      </c>
+      <c r="E13" s="39" t="inlineStr">
+        <is>
+          <t>Total API calls across all concurrent sync operations stay within 50 RPM. The RateLimiter instance is shared (singleton bean), so concurrent threads compete for the same rate budget. Guava RateLimiter is thread-safe — serializes acquire() calls.</t>
+        </is>
+      </c>
+      <c r="F13" s="39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G13" s="39" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="H13" s="39" t="inlineStr">
+        <is>
+          <t>#3401/#3399</t>
+        </is>
+      </c>
+      <c r="I13" s="39" t="inlineStr">
+        <is>
+          <t>PMTool/Sync</t>
+        </is>
+      </c>
+      <c r="J13" s="39" t="inlineStr">
+        <is>
+          <t>Single RateLimiter instance on singleton Spring bean. Thread-safe token-bucket algorithm.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J11"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Admin Panel Test Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>1. Recommended Test Users (Module-Specific)</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="34" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>User / Query</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Use Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Use perekrest or ilnitsky</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Full admin panel access</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Use alsmirnov</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Verify no admin access (negative test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>2. Common Multi-Role Test Users (All Modules)</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="n"/>
+      <c r="C9" s="34" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Best For</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>perekrest</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, CHIEF_ACCOUNTANT, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Best multi-role user (7 roles). Use for cross-role permission testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>pvaynmaster</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, CHIEF_OFFICER, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Multi-role with CHIEF_OFFICER. Use for highest-privilege scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>ilnitsky</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Admin+accountant combo. Use for accounting and admin tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Same role set as ilnitsky. Use as second admin/accountant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>juliet_nekhor</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>DEPT_MGR, EMPLOYEE, HR, PM, VIEW_ALL</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Has VIEW_ALL. Use for read-only permission tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>kcherenkov</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>DEPT_MGR, EMPLOYEE, PM, TECH_LEAD</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Tech Lead + PM. Use for planner/project management tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>alsmirnov</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>EMPLOYEE-only. Use as minimum-privilege baseline user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>3. Common SQL Queries (User Discovery)</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="n"/>
+      <c r="C19" s="34" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>SQL Query</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Find EMPLOYEE-only users (minimum privilege)</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true
+GROUP BY e.id
+HAVING COUNT(*) = 1 AND MAX(r.role) = 'ROLE_EMPLOYEE'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Find active contractors</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_CONTRACTOR'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Find active project managers</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_PROJECT_MANAGER'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Find active accountants</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_ACCOUNTANT'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Find active admins</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_ADMIN'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Get current report/approve periods per office</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>SELECT o.id as office_id, o.name,
+       rp.start as report_period_start,
+       ap.start as approve_period_start
+FROM office o
+JOIN office_period rp ON o.report_period_id = rp.id
+JOIN office_period ap ON o.approve_period_id = ap.id
+ORDER BY o.id;</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>ttt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>4. Module-Specific SQL Queries</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="n"/>
+      <c r="C28" s="34" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>SQL Query</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Find active projects (for project admin tests)</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>SELECT p.id, p.name, p.status, p.customer_name, p.type
+FROM ttt_backend.project p
+WHERE p.status = 'ACTIVE'
+ORDER BY p.name LIMIT 20;</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Find employees by enabled status</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name, e.enabled, e.salary_office
+FROM ttt_backend.employee e
+ORDER BY e.enabled DESC, e.login LIMIT 20;</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Find production calendars and their day counts</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>SELECT c.id, c.name, c.country_code, COUNT(cd.id) as day_count
+FROM ttt_calendar.calendar c
+LEFT JOIN ttt_calendar.calendar_day cd ON c.id = cd.calendar_id
+GROUP BY c.id, c.name, c.country_code
+ORDER BY c.name;</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Find projects with PM Tool links</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>SELECT p.id, p.name, p.pm_tool_id
+FROM ttt_backend.project p
+WHERE p.pm_tool_id IS NOT NULL AND p.status = 'ACTIVE'
+LIMIT 10;</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>List office-to-calendar mappings</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>SELECT o.id as office_id, o.name as office_name, c.name as calendar_name
+FROM ttt_vacation.office o
+LEFT JOIN ttt_calendar.calendar c ON o.calendar_id = c.id
+ORDER BY o.id;</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>5. Data Generation Strategies</t>
+        </is>
+      </c>
+      <c r="B36" s="33" t="n"/>
+      <c r="C36" s="34" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Project creation</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Name: 'Test-' + timestamp (e.g. Test-20260315). Type: COMMERCIAL. Status: defaults to ACTIVE.</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Employee search</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Use login prefix for search filter. Active employees: ~410. Disabled: ~1431.</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Calendar events</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Calendar day types: WORKDAY, PUBLIC_HOLIDAY, SHORTENED_DAY, WEEKEND. Date format: YYYY-MM-DD.</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>6. Environment Reference</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="n"/>
+      <c r="C42" s="34" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>timemachine</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>https://ttt-timemachine.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Primary dev env — has test clock (PATCH to advance time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>qa-1</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>https://ttt-qa-1.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Secondary dev env — real clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>https://ttt-stage.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Production-like env — read-only testing preferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>7. API Authentication</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="n"/>
+      <c r="C48" s="34" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>How to Obtain/Use</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>JWT (user context)</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Login via CAS SSO at /login, extract TTT_JWT_TOKEN cookie. Pass as Authorization: Bearer &lt;token&gt; or Cookie header.</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Most endpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>API token</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Set header API_SECRET_TOKEN: &lt;token_value&gt;. Value from env config file.</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Test/sync endpoints, limited scope</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A48:C48"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>Suite: PM Tool Sprint 15 Integration Cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J3" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>TC-ADM-081</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>PM Tool sync — API pagination handles &gt;100 projects</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>PM Tool has &gt;100 active projects; TTT sync enabled; timemachine env</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>1. Trigger full PM Tool sync via POST /v1/test/project/sync
+2. Monitor sync status — verify paginated fetch with PAGE_SIZE=100
+3. Check pm_sync_status table for completion record
+4. Verify all projects synced (compare PM Tool count vs TTT project count)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Sync completes successfully with multiple page fetches.
+pm_sync_status records show start/end timestamps.
+All PM Tool projects present in TTT project table.</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>#3382</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>PmToolEntitySyncLauncher</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Rate limiter applies per-page: each page fetch calls fetchRateLimiter.acquire()</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>TC-ADM-082</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool sync — id parameter workaround (no ?id= in requests)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool sync enabled; timemachine env</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>1. Trigger sync via POST /v1/test/project/sync
+2. Check application logs for PM Tool API requests
+3. Verify no request uses ?id=N query parameter
+4. Verify PmToolPageRequest is used for all fetches</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>No PM Tool API call uses the id query parameter.
+All requests use the paginated PmToolPageRequest model.
+No 422 Unprocessable Content errors.</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>#3383</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>PmToolClient</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool API docs say id param works but it returns 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>TC-ADM-083</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>PM Tool sync — pmtId persisted and exposed in API</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>PM Tool project has pmtId; TTT sync runs; timemachine env</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>1. Trigger sync via POST /v1/test/project/sync
+2. GET /v1/projects — find a synced project
+3. Verify response contains pmtId field (non-null Long)
+4. Query DB: SELECT pmt_id FROM project WHERE pm_tool_id IS NOT NULL
+5. Verify pmt_id column populated for synced projects</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>API response includes pmtId field.
+DB pmt_id column populated for all PM Tool synced projects.
+pmtId matches PM Tool's internal project ID.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>#3387</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Project / PmToolProjectSynchronizer</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>DB migration V2_1_26 adds pmt_id column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>TC-ADM-084</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool sync — CSToolEntityReference type parsing</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool API returns employee refs as {id: N, type: 'employee'|'sales'|'contractor'}</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>1. Trigger sync with project having mixed employee types
+2. Verify sales-type employees are filtered out from manager, owner, supervisor
+3. Verify sales-type watchers removed from watchersIds list
+4. Verify employee-type and contractor-type employees are processed normally
+5. Check project after sync: no sales employees in any role</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Sales-type employees excluded from all project roles.
+Employee-type and contractor-type processed normally.
+CSToolEntityReference.isSales() correctly identifies sales type (case-insensitive).</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>#3389</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>PmToolProjectSynchronizer / CSToolEntityReference</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>New PM Tool API format: plain integer IDs replaced with {id, type} objects</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>TC-ADM-085</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Admin UI — Project name links to PM Tool via pmtId</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Admin &gt; Projects page; projects synced from PM Tool; timemachine env</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>1. Navigate to Admin &gt; All Projects
+2. Find a project with pmtId (synced from PM Tool)
+3. Verify project name is a clickable hyperlink
+4. Verify link URL: https://pm.noveogroup.com/projects/{pmtId}/profile/general
+5. Find a project WITHOUT pmtId (legacy)
+6. Verify project name is plain text (not a link)</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Synced projects: name is blue hyperlink to PM Tool project page.
+Legacy projects without pmtId: name is plain text.
+Dev env uses pm-dev2 URL; prod uses pm.noveogroup.com.</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>#3093</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Admin / tableHelpers.js</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>isDevelopmentEnv check distinguishes pm-dev2 vs pm.noveogroup.com URLs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>TC-ADM-086</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Admin UI — Create Project button removed</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Admin &gt; Projects page; any user with PROJECTS_ALL permission</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>1. Navigate to Admin &gt; All Projects
+2. Check toolbar for 'Create Project' button
+3. Navigate to Admin &gt; My Projects
+4. Check toolbar for 'Create Project' button
+5. Verify no project creation UI exists anywhere in Admin</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>No 'Create Project' button on All Projects tab.
+No 'Create Project' button on My Projects tab.
+Projects can only be created via PM Tool.</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>#3093</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Admin / TableProjectsButtons.js</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Project creation moved entirely to PM Tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>TC-ADM-087</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Admin UI — Edit Project shows only 3 tracker fields</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Admin &gt; Projects; user with EDIT permission; timemachine env</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>1. Navigate to Admin &gt; All Projects
+2. Click Edit button (pencil icon) on a project
+3. Verify dialog title: 'Edit Tracker Data'
+4. Verify exactly 3 fields: sync script URL, tracker URL, proxy URL
+5. Verify NO fields for: name, customer, country, type, status, model, owner, manager, observers
+6. Edit tracker URL and save — verify change persisted</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Edit dialog shows only 3 link fields.
+All project metadata fields removed from edit.
+Save persists tracker field changes.
+Proxy field includes link to Google Docs setup guide.</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>#3093</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Admin / EditProjectForm.js</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Previous edit form had 10+ fields; now reduced to 3 tracker-related only</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>TC-ADM-088</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Admin UI — Renamed columns: Supervisor and Manager</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Admin &gt; All Projects and My Projects tabs</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>1. Navigate to Admin &gt; All Projects
+2. Verify column header: 'Supervisor' (was 'Senior Manager')
+3. Navigate to Admin &gt; My Projects
+4. Verify column header: 'Manager' (was 'Current Manager')
+5. Open Project Info modal for any project
+6. Verify label: 'Supervisor' (was 'Senior Manager')</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>All Projects tab: 'Supervisor' column header.
+My Projects tab: 'Manager' column header.
+Project Info modal: 'Supervisor' label.
+Sorting and filtering work correctly on renamed columns.</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>#3093</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Admin / tableHelpers.js / InfoProjectModal.js</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Cosmetic rename but affects test case references and user documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>TC-ADM-089</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Admin UI — Inline editing removed from Type/Status columns</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Admin &gt; All Projects; user with EDIT permission</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>1. Navigate to Admin &gt; All Projects
+2. Click on Type column value for any project
+3. Verify NO inline edit dropdown appears
+4. Click on Status column value
+5. Verify NO inline edit dropdown appears
+6. Click on Transfer/Return Project action
+7. Verify action button does NOT exist</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Type column: click does not open inline editor.
+Status column: click does not open inline editor.
+No Transfer/Return Project action in action menu.
+These fields are read-only, managed by PM Tool.</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>#3093</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Admin / ProjectButton components removed</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Inline editing components (ProjectButton) removed from codebase</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>TC-ADM-090</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool sync — startup full sync on application boot</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>TTT application restart; PM Tool sync enabled; timemachine env</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1. Restart TTT application (or deploy new build)
+2. Check logs for TttStartupApplicationListener activity
+3. Verify full PM Tool sync triggered on startup
+4. Check pm_sync_status for sync record at startup time
+5. Verify all PM Tool projects synced correctly</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Full PM Tool sync runs on application startup.
+TttStartupApplicationListener triggers sync.
+pm_sync_status shows startup sync record.
+Projects match PM Tool data after restart.</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>#3083 / !5130</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>TttStartupApplicationListener</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>Added in !5130: ensures data is current after deployment</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>TC-ADM-091</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>PM Tool sync — default sync script auto-assignment</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>New project created in PM Tool; TTT sync runs; timemachine env</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>1. Create a new project in PM Tool (no tracker config)
+2. Trigger TTT sync or wait for cron
+3. GET /v1/projects — find the new project
+4. Verify scriptUrl set to default: 'ttt.noveogroup.com/api/ttt/resource/defaultTaskInfoScript.js'
+5. Check project change history
+6. Verify default script assignment NOT logged as history event</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>New projects get default sync script URL.
+Default script: ttt.noveogroup.com/api/ttt/resource/defaultTaskInfoScript.js.
+No change history entry for default script assignment.</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>#3083 / !5270</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>PmToolProjectSynchronizer</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Default script only for new projects; existing projects keep their scripts</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>TC-ADM-092</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>PM Tool sync — accounting name set once, never updated</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Project synced from PM Tool; PM Tool project renamed; TTT sync runs</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>1. Verify existing synced project has accountingName set
+2. Rename the project in PM Tool
+3. Trigger TTT sync
+4. GET /v1/projects — check the project
+5. Verify 'name' field updated to new PM Tool name
+6. Verify 'accountingName' still has ORIGINAL name (not updated)
+7. For a brand new project: verify accountingName = name on first sync</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>accountingName set from PM Tool name on first sync only.
+Subsequent PM Tool name changes update 'name' but NOT 'accountingName'.
+New projects: accountingName = name on first sync.</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>#3083</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>PmToolProjectSynchronizer / Project</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>accountingName used for billing/invoicing — must remain stable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J15"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -965,7 +3296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -980,246 +3311,254 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>← Back to Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Feature × Test Type Matrix</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Feature Area</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Bug Verification</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Project Management</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B5" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="C4" s="13" t="inlineStr"/>
-      <c r="D4" s="13" t="n">
+      <c r="C5" s="13" t="inlineStr"/>
+      <c r="D5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E5" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="13" t="inlineStr"/>
-      <c r="G4" s="13" t="n">
+      <c r="F5" s="13" t="inlineStr"/>
+      <c r="G5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="13" t="inlineStr"/>
-      <c r="I4" s="14" t="n">
+      <c r="H5" s="13" t="inlineStr"/>
+      <c r="I5" s="14" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Employee Management</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B6" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="15" t="inlineStr"/>
-      <c r="D5" s="15" t="n">
+      <c r="C6" s="15" t="inlineStr"/>
+      <c r="D6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E6" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="15" t="inlineStr"/>
-      <c r="G5" s="15" t="inlineStr"/>
-      <c r="H5" s="15" t="inlineStr"/>
-      <c r="I5" s="16" t="n">
+      <c r="F6" s="15" t="inlineStr"/>
+      <c r="G6" s="15" t="inlineStr"/>
+      <c r="H6" s="15" t="inlineStr"/>
+      <c r="I6" s="16" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>Production Calendars</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B7" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C7" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="13" t="inlineStr"/>
-      <c r="G6" s="13" t="n">
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="13" t="inlineStr"/>
-      <c r="I6" s="14" t="n">
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="14" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Settings, API &amp; Account</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B8" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="15" t="inlineStr"/>
-      <c r="D7" s="15" t="inlineStr"/>
-      <c r="E7" s="15" t="inlineStr"/>
-      <c r="F7" s="15" t="inlineStr"/>
-      <c r="G7" s="15" t="inlineStr"/>
-      <c r="H7" s="15" t="inlineStr"/>
-      <c r="I7" s="16" t="n">
+      <c r="C8" s="15" t="inlineStr"/>
+      <c r="D8" s="15" t="inlineStr"/>
+      <c r="E8" s="15" t="inlineStr"/>
+      <c r="F8" s="15" t="inlineStr"/>
+      <c r="G8" s="15" t="inlineStr"/>
+      <c r="H8" s="15" t="inlineStr"/>
+      <c r="I8" s="16" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Tracker Integration</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="13" t="inlineStr"/>
-      <c r="G8" s="13" t="n">
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
+      <c r="G9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="14" t="n">
+      <c r="H9" s="13" t="inlineStr"/>
+      <c r="I9" s="14" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>API Errors &amp; Permissions</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B10" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C10" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D10" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="15" t="inlineStr"/>
-      <c r="F9" s="15" t="n">
+      <c r="E10" s="15" t="inlineStr"/>
+      <c r="F10" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="15" t="inlineStr"/>
-      <c r="H9" s="15" t="inlineStr"/>
-      <c r="I9" s="16" t="n">
+      <c r="G10" s="15" t="inlineStr"/>
+      <c r="H10" s="15" t="inlineStr"/>
+      <c r="I10" s="16" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B11" s="18" t="n">
         <v>42</v>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C11" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D11" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E11" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F11" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G11" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H11" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I11" s="19" t="n">
         <v>70</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:I10"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1232,7 +3571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1244,186 +3583,161 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>← Back to Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Risk Assessment — Administration Module</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Likelihood</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Mitigation / Test Focus</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>Project DELETE</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>AUTHENTICATED_USER on DELETE endpoint — any authenticated user reaches service layer</t>
-        </is>
-      </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>TC-ADM-014: Verify ProjectPermissionService enforces DELETE. TC-ADM-061: Permission hierarchy test.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
         <is>
-          <t>Employee PATCH</t>
+          <t>Project DELETE</t>
         </is>
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>Missing @PreAuthorize on PATCH /{login} — controller allows any request through</t>
+          <t>AUTHENTICATED_USER on DELETE endpoint — any authenticated user reaches service layer</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t>TC-ADM-029: Test unauthenticated PATCH. Verify service-level guards catch unauthorized access.</t>
+          <t>TC-ADM-014: Verify ProjectPermissionService enforces DELETE. TC-ADM-061: Permission hierarchy test.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
         <is>
+          <t>Employee PATCH</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Missing @PreAuthorize on PATCH /{login} — controller allows any request through</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>TC-ADM-029: Test unauthenticated PATCH. Verify service-level guards catch unauthorized access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
           <t>Calendar cascade</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Calendar event deletion triggers vacation/day-off recalculation across services</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>TC-ADM-040: Delete event and verify cascade. TC-ADM-042: Working days recalculation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>PM Tool sync failure</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>Missing employees → IllegalStateException → HTTP 500</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
-        <is>
-          <t>TC-ADM-020: Trigger sync with missing CS IDs. Verify error handling.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>PM Tool rate limiting</t>
+          <t>PM Tool sync failure</t>
         </is>
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Aggressive sync may exceed rate limit, blocking other API calls</t>
+          <t>Missing employees → IllegalStateException → HTTP 500</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -1438,31 +3752,31 @@
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>TC-ADM-016: Verify rate limiter (50 req/min). TC-ADM-021: Failed entity retry batching.</t>
+          <t>TC-ADM-020: Trigger sync with missing CS IDs. Verify error handling.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>Calendar name uniqueness</t>
+          <t>PM Tool rate limiting</t>
         </is>
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Frontend case-insensitive but backend may be case-sensitive — bypass creates near-duplicates</t>
+          <t>Aggressive sync may exceed rate limit, blocking other API calls</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -1470,31 +3784,31 @@
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>TC-ADM-034: Test case sensitivity gap.</t>
+          <t>TC-ADM-016: Verify rate limiter (50 req/min). TC-ADM-021: Failed entity retry batching.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>GraalVM sandbox bypass</t>
+          <t>Calendar name uniqueness</t>
         </is>
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>Loop prevention via string matching (not AST) — potentially fragile</t>
+          <t>Frontend case-insensitive but backend may be case-sensitive — bypass creates near-duplicates</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -1502,19 +3816,19 @@
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>TC-ADM-058: Test sandbox security boundaries. Test creative loop constructs.</t>
+          <t>TC-ADM-034: Test case sensitivity gap.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>Tracker credential encryption</t>
+          <t>GraalVM sandbox bypass</t>
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>Encrypted credentials stored in DB — key management not visible</t>
+          <t>Loop prevention via string matching (not AST) — potentially fragile</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -1534,115 +3848,115 @@
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>TC-ADM-051/054: Credential lifecycle. Verify encrypted storage.</t>
+          <t>TC-ADM-058: Test sandbox security boundaries. Test creative loop constructs.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
+          <t>Tracker credential encryption</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Encrypted credentials stored in DB — key management not visible</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>TC-ADM-051/054: Credential lifecycle. Verify encrypted storage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
           <t>Work log sync data volume</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>222K tracker work log rows — bulk sync may timeout</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>TC-ADM-057: Bidirectional sync. TC-ADM-021: Timeout handling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>Calendar PATCH asymmetry</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>Event PATCH only updates reason — users may expect duration/date editable</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>TC-ADM-039: Verify only reason updated on PATCH.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>Draft → ACTIVE mapping</t>
+          <t>Calendar PATCH asymmetry</t>
         </is>
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>PM Tool draft projects silently become ACTIVE in TTT</t>
+          <t>Event PATCH only updates reason — users may expect duration/date editable</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>TC-ADM-018: Verify mapping.</t>
+          <t>TC-ADM-039: Verify only reason updated on PATCH.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>Role naming inconsistency</t>
+          <t>Draft → ACTIVE mapping</t>
         </is>
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>'ADMIN' vs 'ROLE_CHIEF_ACCOUNTANT' — inconsistent Spring Security convention</t>
+          <t>PM Tool draft projects silently become ACTIVE in TTT</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -1662,37 +3976,69 @@
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t>TC-ADM-037: Verify both role formats work.</t>
+          <t>TC-ADM-018: Verify mapping.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
         <is>
+          <t>Role naming inconsistency</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>'ADMIN' vs 'ROLE_CHIEF_ACCOUNTANT' — inconsistent Spring Security convention</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>TC-ADM-037: Verify both role formats work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
           <t>findByDate null response</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>Returns null instead of 404 — clients may not handle null</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>TC-ADM-041: Verify null response for missing dates.</t>
         </is>
@@ -1701,8 +4047,11 @@
   </sheetData>
   <autoFilter ref="A3:F16"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
